--- a/final_project_demo/scholarships_data_collection_template.xlsx
+++ b/final_project_demo/scholarships_data_collection_template.xlsx
@@ -8,38 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z0021rfv\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B400108-69CB-4304-A791-76C5AC056383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{399F5709-3372-43F6-AD58-307F4038CA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49EACDF-8F30-4BCF-88B9-DC3EF12A9DB1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
+    <sheet name="Sources &amp; Notes" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="130">
   <si>
     <t>Scholarship name</t>
   </si>
@@ -126,13 +108,321 @@
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>Tennessee Promise Scholarship (TN Promise)</t>
+  </si>
+  <si>
+    <t>Tennessee Higher Education Commission (THEC) / Tennessee Student Assistance Corporation</t>
+  </si>
+  <si>
+    <t>Government agency</t>
+  </si>
+  <si>
+    <t>https://www.tn.gov/tnpromise.html</t>
+  </si>
+  <si>
+    <t>Web search; THEC press release (Aug 11, 2026); CollegeforTN.org</t>
+  </si>
+  <si>
+    <t>Tennessee (South)</t>
+  </si>
+  <si>
+    <t>State/local</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>High school</t>
+  </si>
+  <si>
+    <t>Last-dollar tuition scholarship (state program)</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>Varies (covers tuition &amp; mandatory fees not paid by Pell, HOPE or TSAA)</t>
+  </si>
+  <si>
+    <t>No fixed cap (67,000+ seniors applied for Class of 2026)</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Varies</t>
+  </si>
+  <si>
+    <t>Unknown (already open as of 2026-08-11)</t>
+  </si>
+  <si>
+    <t>Tennessee high school senior (public, private or home school), Class of 2027</t>
+  </si>
+  <si>
+    <t>None stated</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>No (FAFSA required)</t>
+  </si>
+  <si>
+    <t>Yes (service required to keep award)</t>
+  </si>
+  <si>
+    <t>Complete FAFSA by the posted deadline; attend mandatory mentor/orientation meetings; use at an eligible TN community college, TCAT or other eligible institution</t>
+  </si>
+  <si>
+    <t>Online - THEC Student Portal (CollegeforTN.org/tnpromise)</t>
+  </si>
+  <si>
+    <t>Last-dollar program, so the dollar value depends on other aid received. Deadline is from THEC release of 2026-08-11. Renewal rules and exact service hours not confirmed - students should check the official page.</t>
+  </si>
+  <si>
+    <t>Minnesota Masonic Charities Signature Scholarship</t>
+  </si>
+  <si>
+    <t>Minnesota Masonic Charities</t>
+  </si>
+  <si>
+    <t>Foundation/nonprofit</t>
+  </si>
+  <si>
+    <t>https://mnmasoniccharities.org/programs/scholarships/</t>
+  </si>
+  <si>
+    <t>Scholarships360 / Scholarships.com / Niche (discovery); details verified on provider site</t>
+  </si>
+  <si>
+    <t>Minnesota (Midwest)</t>
+  </si>
+  <si>
+    <t>Merit-based</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Not posted on official page (aggregators list 2027-02-28 - unverified)</t>
+  </si>
+  <si>
+    <t>Minnesota high school or home school student; must attend a Minnesota college/university</t>
+  </si>
+  <si>
+    <t>Unknown (aggregator lists a 300-word essay)</t>
+  </si>
+  <si>
+    <t>Unknown (provider FAQ mentions recommendation letters)</t>
+  </si>
+  <si>
+    <t>Transcript only (ACT no longer required)</t>
+  </si>
+  <si>
+    <t>Masonic affiliation NOT required; committee looks for good character and school/community involvement</t>
+  </si>
+  <si>
+    <t>Online - Submittable (mmc.submittable.com)</t>
+  </si>
+  <si>
+    <t>$5,000 per year, renewable for up to 3 additional years (4 years x $5,000 = $20,000). Older aggregator listings show $6,000 / 6 awards / ACT required - outdated; official page shows $5,000 / 10 awards. Good example of conflicting sources.</t>
+  </si>
+  <si>
+    <t>TASB Governance Camp Student Voice Scholarship</t>
+  </si>
+  <si>
+    <t>Texas Association of School Boards (TASB); sponsored by Walsh Gallegos</t>
+  </si>
+  <si>
+    <t>Professional association</t>
+  </si>
+  <si>
+    <t>https://www.tasb.org/training-events/governance-camp</t>
+  </si>
+  <si>
+    <t>Texas Comptroller scholarship listing; details verified on TASB site</t>
+  </si>
+  <si>
+    <t>Texas (South)</t>
+  </si>
+  <si>
+    <t>Leadership / student voice</t>
+  </si>
+  <si>
+    <t>Public education / civic leadership</t>
+  </si>
+  <si>
+    <t>Current senior at a Texas public high school</t>
+  </si>
+  <si>
+    <t>Recipients must attend Governance Camp (Galveston, Mar 3-6, 2027) and take part in the Student Panel</t>
+  </si>
+  <si>
+    <t>Online application via tasb.org (reminder sign-up available)</t>
+  </si>
+  <si>
+    <t>Deadline is 5 p.m. on 2027-01-15. Hotel, travel and meals (within an allowance) are also covered. Application contents are not listed on the public page - students should record them once the application opens.</t>
+  </si>
+  <si>
+    <t>Cal Grant (High School Entitlement Award)</t>
+  </si>
+  <si>
+    <t>California Student Aid Commission (CSAC)</t>
+  </si>
+  <si>
+    <t>https://www.csac.ca.gov/cal-grant</t>
+  </si>
+  <si>
+    <t>Web search; CSAC "How to Apply" page; LAO budget analysis (award amounts)</t>
+  </si>
+  <si>
+    <t>California (West)</t>
+  </si>
+  <si>
+    <t>Need-based state grant</t>
+  </si>
+  <si>
+    <t>Up to $15,588 per year (UC tuition award, 2026-27 rates); varies by award type and school</t>
+  </si>
+  <si>
+    <t>Entitlement - all eligible applicants</t>
+  </si>
+  <si>
+    <t>California resident</t>
+  </si>
+  <si>
+    <t>2.0 (Cal Grant B) / 3.0 (Cal Grant A)</t>
+  </si>
+  <si>
+    <t>Verified GPA sent to CSAC; no test score</t>
+  </si>
+  <si>
+    <t>Submit FAFSA or California Dream Act Application (CADAA) AND a verified Cal Grant GPA by the deadline; household income/asset ceilings apply</t>
+  </si>
+  <si>
+    <t>FAFSA or CADAA (no separate Cal Grant form)</t>
+  </si>
+  <si>
+    <t>Open date = FAFSA/CADAA availability (Oct 1, 2026). Max potential value is an ESTIMATE: 4 years x $15,588 (2026-27 UC tuition award); first-year Cal Grant B students generally get only the $1,648 access award. Classified as an educational award from a state agency.</t>
+  </si>
+  <si>
+    <t>Jack Kent Cooke Foundation Young Scholars Program</t>
+  </si>
+  <si>
+    <t>Jack Kent Cooke Foundation</t>
+  </si>
+  <si>
+    <t>https://www.jkcf.org/our-scholarships/young-scholars-program/</t>
+  </si>
+  <si>
+    <t>Unigo (discovery); details verified on jkcf.org (FAQ and Young Scholars profile PDF)</t>
+  </si>
+  <si>
+    <t>National (all U.S. states)</t>
+  </si>
+  <si>
+    <t>National</t>
+  </si>
+  <si>
+    <t>7 (apply in 7th grade; support runs from 8th through 12th grade)</t>
+  </si>
+  <si>
+    <t>Middle school</t>
+  </si>
+  <si>
+    <t>Merit + need-based (academic enrichment and advising)</t>
+  </si>
+  <si>
+    <t>Not published (funds enrichment programs, tutoring, technology, summer programs and advising)</t>
+  </si>
+  <si>
+    <t>Unknown (2026 cycle opened 2026-02-05)</t>
+  </si>
+  <si>
+    <t>Attending a U.S. middle school and planning to attend a U.S. high school (no state restriction)</t>
+  </si>
+  <si>
+    <t>All or mostly As; no Cs in core subjects since start of 6th grade</t>
+  </si>
+  <si>
+    <t>Yes (3 short answers of 200 words + one 350-word essay)</t>
+  </si>
+  <si>
+    <t>Yes (2 online teacher forms)</t>
+  </si>
+  <si>
+    <t>Report cards (6th &amp; 7th grade); no test scores</t>
+  </si>
+  <si>
+    <t>Yes (scored selection criterion)</t>
+  </si>
+  <si>
+    <t>Family adjusted gross income up to $95,000 (median of last cohort about $49,000); full financial review of finalists</t>
+  </si>
+  <si>
+    <t>Online application portal (link posted at jkcf.org when open)</t>
+  </si>
+  <si>
+    <t>Number of awards is the 2025 cohort size (varies yearly). Funding starts the summer before 9th grade. 2027 deadline is from the official FAQ; the 2026 cycle closed 2026-04-29, so students should plan ahead. One of the few middle-school scholarships in the sample.</t>
+  </si>
+  <si>
+    <t>SAMPLE DATA - 5 scholarships (TN, MN, TX, CA + 1 national) for the Pathways to Scholarships final project</t>
+  </si>
+  <si>
+    <t>Verified on 2026-10-01. Deadlines and amounts change every cycle - students must re-verify on the official page before submitting their own data.</t>
+  </si>
+  <si>
+    <t>How to read the Sheet2 rows</t>
+  </si>
+  <si>
+    <t>Each row = one scholarship. "Unknown" = checked, but not stated publicly. "No" = the provider's page shows it is not required. Dates are real Excel dates (yyyy-mm-dd) where a date was found; otherwise text.</t>
+  </si>
+  <si>
+    <t>Some cells intentionally hold text (e.g., "Varies") instead of numbers - students will clean/standardize these in Phase 2 (EDA).</t>
+  </si>
+  <si>
+    <t>Official sources used (provider pages first)</t>
+  </si>
+  <si>
+    <t>Tennessee Promise: https://www.tn.gov/tnpromise.html ; THEC press release (Aug 11, 2026): https://www.tn.gov/content/dam/tn/thec/news/news_media/2026/Press%20Release%20THEC%20Direct%20Admissions.pdf</t>
+  </si>
+  <si>
+    <t>Minnesota Masonic Charities: https://mnmasoniccharities.org/programs/scholarships/ ; FAQ: https://mnmasoniccharities.org/about/scholarship-frequently-asked-questions/</t>
+  </si>
+  <si>
+    <t>TASB Governance Camp Student Scholarship: https://www.tasb.org/training-events/governance-camp</t>
+  </si>
+  <si>
+    <t>Cal Grant: https://www.csac.ca.gov/apply (deadline) ; https://www.csac.ca.gov/cal-grant ; award amounts: https://lao.ca.gov/Education/EdBudget/Details/1080</t>
+  </si>
+  <si>
+    <t>Jack Kent Cooke Young Scholars: https://www.jkcf.org/our-scholarships/young-scholars-program/faqs/ ; profile PDF: https://www.jkcf.org/wp-content/uploads/2026/02/2026-JKCF-YS-Profile-JAN-v3d.pdf</t>
+  </si>
+  <si>
+    <t>Discovery-only sources (not relied on for final values)</t>
+  </si>
+  <si>
+    <t>Scholarships360, Scholarships.com, Niche, Unigo, BigFuture - useful for finding scholarships, but several showed outdated amounts/deadlines (e.g., Minnesota Masonic Signature Scholarship).</t>
+  </si>
+  <si>
+    <t>Teaching points built into the sample</t>
+  </si>
+  <si>
+    <t>1) Conflicting sources (MN). 2) Variable / last-dollar awards with no fixed dollar value (TN, CA, JKCF). 3) Deadlines not yet posted (MN). 4) A middle-school scholarship (JKCF) vs. four high-school ones. 5) Need-based vs. merit-based mix. 6) Closed 2026 cycle with a known 2027 deadline (JKCF).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="\$#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,20 +432,30 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -163,14 +463,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -505,34 +838,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7E4C1B2-2FAE-4678-9C42-073E3B925164}">
-  <dimension ref="A1:AC1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="17" max="17" width="22" customWidth="1"/>
+    <col min="18" max="18" width="32" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="22" width="22" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="24" customWidth="1"/>
+    <col min="24" max="24" width="20" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="40" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="28" customWidth="1"/>
+    <col min="28" max="28" width="14" customWidth="1"/>
+    <col min="29" max="29" width="55" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="105" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -621,8 +961,553 @@
         <v>28</v>
       </c>
     </row>
+    <row r="2" spans="1:29" ht="60" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>46328</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>46296</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="75" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" s="4">
+        <v>5000</v>
+      </c>
+      <c r="M3" s="2">
+        <v>10</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O3" s="4">
+        <v>20000</v>
+      </c>
+      <c r="P3" s="3">
+        <v>46388</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="S3" s="5">
+        <v>3</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>46296</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="60" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" s="4">
+        <v>1500</v>
+      </c>
+      <c r="M4" s="2">
+        <v>5</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O4" s="4">
+        <v>1500</v>
+      </c>
+      <c r="P4" s="3">
+        <v>46371</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>46402</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>46296</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="75" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O5" s="4">
+        <v>62352</v>
+      </c>
+      <c r="P5" s="3">
+        <v>46296</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>46448</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>46296</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="75" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="M6" s="2">
+        <v>65</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>46505</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>46296</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:A19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="140" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+    </row>
+    <row r="4" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+    </row>
+    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+    </row>
+    <row r="15" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+    </row>
+    <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="30" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
